--- a/12600637.xlsx
+++ b/12600637.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8918523-4731-4CBC-8EA6-F53A4D37CA4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF3C59E-A466-46F1-8AF7-27251F9D293F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2743,46 +2743,86 @@
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B47" s="14">
+        <v>540</v>
+      </c>
+      <c r="C47" s="14">
+        <v>0</v>
+      </c>
+      <c r="D47" s="14">
+        <v>120</v>
+      </c>
+      <c r="E47" s="14">
+        <v>90</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>100</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>850</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
+        <v>590</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="M47" s="16"/>
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B48" s="14">
+        <v>420</v>
+      </c>
+      <c r="C48" s="14">
+        <v>0</v>
+      </c>
+      <c r="D48" s="14">
+        <v>120</v>
+      </c>
+      <c r="E48" s="14">
+        <v>90</v>
+      </c>
+      <c r="F48" s="14">
+        <v>200</v>
+      </c>
+      <c r="G48" s="14">
+        <v>4</v>
+      </c>
+      <c r="H48" s="14">
+        <v>60</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>890</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
+        <v>550</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="M48" s="16"/>
       <c r="N48" s="17"/>
     </row>

--- a/12600637.xlsx
+++ b/12600637.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF3C59E-A466-46F1-8AF7-27251F9D293F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979CEBA8-8147-488C-A5D8-CD53D0756B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>low</t>
   </si>
 </sst>
 </file>
@@ -2827,24 +2830,44 @@
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B49" s="14">
+        <v>420</v>
+      </c>
+      <c r="C49" s="14">
+        <v>45</v>
+      </c>
+      <c r="D49" s="14">
+        <v>30</v>
+      </c>
+      <c r="E49" s="14">
+        <v>60</v>
+      </c>
+      <c r="F49" s="14">
+        <v>350</v>
+      </c>
+      <c r="G49" s="14">
+        <v>7</v>
+      </c>
+      <c r="H49" s="14">
+        <v>0</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>905</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
+        <v>535</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M49" s="16"/>
       <c r="N49" s="17"/>
     </row>

--- a/12600637.xlsx
+++ b/12600637.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979CEBA8-8147-488C-A5D8-CD53D0756B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D01A918-7807-454D-97DD-88FDB9492621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2872,24 +2872,44 @@
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B50" s="14">
+        <v>420</v>
+      </c>
+      <c r="C50" s="14">
+        <v>45</v>
+      </c>
+      <c r="D50" s="14">
+        <v>100</v>
+      </c>
+      <c r="E50" s="14">
+        <v>30</v>
+      </c>
+      <c r="F50" s="14">
+        <v>300</v>
+      </c>
+      <c r="G50" s="14">
+        <v>6</v>
+      </c>
+      <c r="H50" s="14">
+        <v>0</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>895</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
+        <v>545</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M50" s="16"/>
       <c r="N50" s="17"/>
     </row>

--- a/12600637.xlsx
+++ b/12600637.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D01A918-7807-454D-97DD-88FDB9492621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A744121-D51A-46B0-A198-1DE4AE9177C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2914,24 +2914,44 @@
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B51" s="14">
+        <v>420</v>
+      </c>
+      <c r="C51" s="14">
+        <v>45</v>
+      </c>
+      <c r="D51" s="14">
+        <v>60</v>
+      </c>
+      <c r="E51" s="14">
+        <v>30</v>
+      </c>
+      <c r="F51" s="14">
+        <v>200</v>
+      </c>
+      <c r="G51" s="14">
+        <v>2</v>
+      </c>
+      <c r="H51" s="14">
+        <v>120</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>875</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
+        <v>565</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="M51" s="16"/>
       <c r="N51" s="17"/>
     </row>

--- a/12600637.xlsx
+++ b/12600637.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A744121-D51A-46B0-A198-1DE4AE9177C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BD24EF-8B33-45D0-A1B6-4247842E9DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2956,24 +2956,44 @@
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B52" s="14">
+        <v>420</v>
+      </c>
+      <c r="C52" s="14">
+        <v>45</v>
+      </c>
+      <c r="D52" s="14">
+        <v>100</v>
+      </c>
+      <c r="E52" s="14">
+        <v>45</v>
+      </c>
+      <c r="F52" s="14">
+        <v>300</v>
+      </c>
+      <c r="G52" s="14">
+        <v>5</v>
+      </c>
+      <c r="H52" s="14">
+        <v>100</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
+        <v>430</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M52" s="16"/>
       <c r="N52" s="17"/>
     </row>

--- a/12600637.xlsx
+++ b/12600637.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BD24EF-8B33-45D0-A1B6-4247842E9DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C3A48F-8D99-4305-BF97-3E48E35CD08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -353,7 +353,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -376,11 +376,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -420,6 +431,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -907,74 +921,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12600637</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1198,6 +1212,9 @@
       <c r="A10" s="13">
         <v>46248</v>
       </c>
+      <c r="B10" s="18">
+        <v>420</v>
+      </c>
       <c r="C10" s="14">
         <v>0</v>
       </c>
@@ -1218,11 +1235,11 @@
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>450</v>
+        <v>870</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>990</v>
+        <v>570</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>49</v>
@@ -2998,24 +3015,44 @@
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>45926</v>
+      </c>
+      <c r="B53" s="14">
+        <v>540</v>
+      </c>
+      <c r="C53" s="14">
+        <v>45</v>
+      </c>
+      <c r="D53" s="14">
+        <v>100</v>
+      </c>
+      <c r="E53" s="14">
+        <v>60</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>100</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>845</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
+        <v>595</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M53" s="16"/>
       <c r="N53" s="17"/>
     </row>

--- a/12600637.xlsx
+++ b/12600637.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C3A48F-8D99-4305-BF97-3E48E35CD08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A08D5C9-5377-44A7-BAF4-C999CDCFB1C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>low</t>
+  </si>
+  <si>
+    <t>bad</t>
   </si>
 </sst>
 </file>
@@ -3057,51 +3060,93 @@
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>45927</v>
+      </c>
+      <c r="B54" s="14">
+        <v>520</v>
+      </c>
+      <c r="C54" s="14">
+        <v>0</v>
+      </c>
+      <c r="D54" s="14">
+        <v>0</v>
+      </c>
+      <c r="E54" s="14">
+        <v>45</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>100</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>665</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
+        <v>775</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="M54" s="16"/>
       <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>45928</v>
+      </c>
+      <c r="B55" s="14">
+        <v>240</v>
+      </c>
+      <c r="C55" s="14">
+        <v>0</v>
+      </c>
+      <c r="D55" s="14">
+        <v>0</v>
+      </c>
+      <c r="E55" s="14">
+        <v>0</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>100</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>340</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
+        <v>1100</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>62</v>
+      </c>
       <c r="M55" s="16"/>
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
+      <c r="A56" s="13">
+        <v>45929</v>
+      </c>
       <c r="B56" s="14"/>
       <c r="C56" s="14"/>
       <c r="D56" s="14"/>
@@ -3118,7 +3163,9 @@
         <v/>
       </c>
       <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
+      <c r="L56" s="16" t="s">
+        <v>63</v>
+      </c>
       <c r="M56" s="16"/>
       <c r="N56" s="17"/>
     </row>

--- a/12600637.xlsx
+++ b/12600637.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A08D5C9-5377-44A7-BAF4-C999CDCFB1C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B3D84B-BB7B-4E06-AA9F-3BF94A67A3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3147,22 +3147,38 @@
       <c r="A56" s="13">
         <v>45929</v>
       </c>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="B56" s="14">
+        <v>240</v>
+      </c>
+      <c r="C56" s="14">
+        <v>0</v>
+      </c>
+      <c r="D56" s="14">
+        <v>0</v>
+      </c>
+      <c r="E56" s="14">
+        <v>0</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>0</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>240</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
+        <v>1200</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>69</v>
+      </c>
       <c r="L56" s="16" t="s">
         <v>63</v>
       </c>
@@ -3170,24 +3186,44 @@
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>45930</v>
+      </c>
+      <c r="B57" s="14">
+        <v>240</v>
+      </c>
+      <c r="C57" s="14">
+        <v>0</v>
+      </c>
+      <c r="D57" s="14">
+        <v>0</v>
+      </c>
+      <c r="E57" s="14">
+        <v>0</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>0</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>240</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
+        <v>1200</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>63</v>
+      </c>
       <c r="M57" s="16"/>
       <c r="N57" s="17"/>
     </row>

--- a/12600637.xlsx
+++ b/12600637.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B3D84B-BB7B-4E06-AA9F-3BF94A67A3DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D84DFB7-D2FB-42C6-95D2-8962C64C0DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>bad</t>
+  </si>
+  <si>
+    <t>High</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +1169,9 @@
       <c r="L8" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M8" s="16"/>
+      <c r="M8" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N8" s="17"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1292,7 +1297,9 @@
       <c r="L11" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M11" s="16"/>
+      <c r="M11" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="N11" s="17"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1586,7 +1593,9 @@
       <c r="L18" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M18" s="16"/>
+      <c r="M18" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="N18" s="17"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1628,7 +1637,9 @@
       <c r="L19" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M19" s="16"/>
+      <c r="M19" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N19" s="17"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1712,7 +1723,9 @@
       <c r="L21" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M21" s="16"/>
+      <c r="M21" s="16" t="s">
+        <v>67</v>
+      </c>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1838,7 +1851,9 @@
       <c r="L24" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M24" s="16"/>
+      <c r="M24" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -2300,7 +2315,9 @@
       <c r="L35" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M35" s="16"/>
+      <c r="M35" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
@@ -2384,7 +2401,9 @@
       <c r="L37" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M37" s="16"/>
+      <c r="M37" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -2426,7 +2445,9 @@
       <c r="L38" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M38" s="16"/>
+      <c r="M38" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -2468,7 +2489,9 @@
       <c r="L39" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M39" s="16"/>
+      <c r="M39" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
@@ -2678,7 +2701,9 @@
       <c r="L44" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M44" s="16"/>
+      <c r="M44" s="16" t="s">
+        <v>67</v>
+      </c>
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
@@ -2711,7 +2736,7 @@
         <v>920</v>
       </c>
       <c r="J45" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I45="","",1440-I45)</f>
         <v>520</v>
       </c>
       <c r="K45" s="16" t="s">
@@ -2804,7 +2829,9 @@
       <c r="L47" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M47" s="16"/>
+      <c r="M47" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
@@ -3140,7 +3167,9 @@
       <c r="L55" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="M55" s="16"/>
+      <c r="M55" s="16" t="s">
+        <v>67</v>
+      </c>
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">

--- a/12600637.xlsx
+++ b/12600637.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\satya\Desktop\datasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D84DFB7-D2FB-42C6-95D2-8962C64C0DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA503C6-5156-4EED-ABA2-34B15E273439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -530,6 +530,9 @@
       <rgbColor rgb="00333399"/>
       <rgbColor rgb="00333333"/>
     </indexedColors>
+    <mruColors>
+      <color rgb="FFFACDA8"/>
+    </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1213,7 +1216,9 @@
       <c r="L9" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M9" s="16"/>
+      <c r="M9" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N9" s="17"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1255,14 +1260,16 @@
       <c r="L10" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M10" s="16"/>
+      <c r="M10" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N10" s="17"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="13">
         <v>46249</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="18">
         <v>480</v>
       </c>
       <c r="C11" s="14">
@@ -1354,7 +1361,7 @@
       <c r="C13" s="14">
         <v>0</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="14">
         <v>120</v>
       </c>
       <c r="E13" s="14">
@@ -1383,7 +1390,9 @@
       <c r="L13" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M13" s="16"/>
+      <c r="M13" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="N13" s="17"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
@@ -1425,7 +1434,9 @@
       <c r="L14" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M14" s="16"/>
+      <c r="M14" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="N14" s="17"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1467,7 +1478,9 @@
       <c r="L15" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M15" s="16"/>
+      <c r="M15" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="N15" s="17"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1509,7 +1522,9 @@
       <c r="L16" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M16" s="16"/>
+      <c r="M16" s="16" t="s">
+        <v>70</v>
+      </c>
       <c r="N16" s="17"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1551,7 +1566,9 @@
       <c r="L17" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M17" s="16"/>
+      <c r="M17" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N17" s="17"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
@@ -1681,7 +1698,9 @@
       <c r="L20" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="M20" s="16"/>
+      <c r="M20" s="16" t="s">
+        <v>68</v>
+      </c>
       <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
@@ -1767,7 +1786,9 @@
       <c r="L22" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M22" s="16"/>
+      <c r="M22" s="16" t="s">
+        <v>68</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
@@ -1809,7 +1830,9 @@
       <c r="L23" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="M23" s="16"/>
+      <c r="M23" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -1895,7 +1918,9 @@
       <c r="L25" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M25" s="16"/>
+      <c r="M25" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -1937,7 +1962,9 @@
       <c r="L26" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M26" s="16"/>
+      <c r="M26" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -1979,7 +2006,9 @@
       <c r="L27" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M27" s="16"/>
+      <c r="M27" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2021,7 +2050,9 @@
       <c r="L28" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M28" s="16"/>
+      <c r="M28" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2063,7 +2094,9 @@
       <c r="L29" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M29" s="16"/>
+      <c r="M29" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
@@ -2105,7 +2138,9 @@
       <c r="L30" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M30" s="16"/>
+      <c r="M30" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2147,7 +2182,9 @@
       <c r="L31" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M31" s="16"/>
+      <c r="M31" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2189,7 +2226,9 @@
       <c r="L32" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="M32" s="16"/>
+      <c r="M32" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
@@ -2231,7 +2270,9 @@
       <c r="L33" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M33" s="16"/>
+      <c r="M33" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -2273,7 +2314,9 @@
       <c r="L34" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M34" s="16"/>
+      <c r="M34" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
@@ -2359,7 +2402,9 @@
       <c r="L36" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M36" s="16"/>
+      <c r="M36" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
@@ -2533,7 +2578,9 @@
       <c r="L40" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M40" s="16"/>
+      <c r="M40" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -2575,7 +2622,9 @@
       <c r="L41" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M41" s="16"/>
+      <c r="M41" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
@@ -2617,7 +2666,9 @@
       <c r="L42" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M42" s="16"/>
+      <c r="M42" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
@@ -2659,7 +2710,9 @@
       <c r="L43" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M43" s="16"/>
+      <c r="M43" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
@@ -2745,7 +2798,9 @@
       <c r="L45" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M45" s="16"/>
+      <c r="M45" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
@@ -2787,7 +2842,9 @@
       <c r="L46" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M46" s="16"/>
+      <c r="M46" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
@@ -2873,7 +2930,9 @@
       <c r="L48" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M48" s="16"/>
+      <c r="M48" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
@@ -2915,7 +2974,9 @@
       <c r="L49" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M49" s="16"/>
+      <c r="M49" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
@@ -2957,7 +3018,9 @@
       <c r="L50" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M50" s="16"/>
+      <c r="M50" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
@@ -2999,7 +3062,9 @@
       <c r="L51" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="M51" s="16"/>
+      <c r="M51" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
@@ -3041,7 +3106,9 @@
       <c r="L52" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M52" s="16"/>
+      <c r="M52" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -3083,7 +3150,9 @@
       <c r="L53" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M53" s="16"/>
+      <c r="M53" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
@@ -3125,7 +3194,9 @@
       <c r="L54" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M54" s="16"/>
+      <c r="M54" s="16" t="s">
+        <v>50</v>
+      </c>
       <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
@@ -3211,7 +3282,9 @@
       <c r="L56" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M56" s="16"/>
+      <c r="M56" s="16" t="s">
+        <v>68</v>
+      </c>
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
@@ -3253,7 +3326,9 @@
       <c r="L57" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="M57" s="16"/>
+      <c r="M57" s="16" t="s">
+        <v>68</v>
+      </c>
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
@@ -10853,6 +10928,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>